--- a/output/pdf_financials_xlsx/NOP.xlsx
+++ b/output/pdf_financials_xlsx/NOP.xlsx
@@ -1931,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0706</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.091014</v>
       </c>
     </row>
     <row r="93">
@@ -3137,7 +3137,11 @@
           <t>Reserve for warrants (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3352,7 +3356,11 @@
           <t>Reserve for warrants (Note 8)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NOP.xlsx
+++ b/output/pdf_financials_xlsx/NOP.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.202</v>
+        <v>0.929943</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.400507</v>
+        <v>0.898759</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.273594</v>
+        <v>0.6100179999999999</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.202</v>
+        <v>-0.929943</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.400507</v>
+        <v>-0.898759</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.273594</v>
+        <v>-0.6100179999999999</v>
       </c>
     </row>
     <row r="12">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.334802</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.039176</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.008312</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.334802</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.039176</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.008312</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.453215</v>
+        <v>0.118413</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.062932</v>
+        <v>0.023756</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.013863</v>
+        <v>0.005551</v>
       </c>
     </row>
     <row r="49">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>-0.929943</v>
+        <v>0.929943</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>-0.898759</v>
+        <v>0.898759</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.6100179999999999</v>
+        <v>0.6100179999999999</v>
       </c>
     </row>
     <row r="102">

--- a/output/pdf_financials_xlsx/NOP.xlsx
+++ b/output/pdf_financials_xlsx/NOP.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.137021</v>
+        <v>0.145271</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.267575</v>
+        <v>0.278575</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.213611</v>
+        <v>0.221111</v>
       </c>
     </row>
     <row r="8">
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.005842</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.008186000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.173901</v>
+        <v>0.179743</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.04229</v>
+        <v>0.050476</v>
       </c>
     </row>
     <row r="107">
@@ -3670,7 +3670,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-0.011364</v>
       </c>
@@ -5483,7 +5487,11 @@
           <t>Directors’ fees (Note 10)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -5996,7 +6004,11 @@
           <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>0.00825</v>
       </c>
